--- a/thaiprint-website/ThaiPrint-Calculator-Offline.xlsx
+++ b/thaiprint-website/ThaiPrint-Calculator-Offline.xlsx
@@ -10,20 +10,24 @@
     <sheet name="Prices" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Offset" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Inkjet" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Quote" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Quote'!$A$1:$E$27</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="฿#,##0.00"/>
     <numFmt numFmtId="166" formatCode="฿#,##0.0000"/>
+    <numFmt numFmtId="167" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,6 +60,23 @@
       <b val="1"/>
       <color rgb="00C0504D"/>
       <sz val="20"/>
+    </font>
+    <font>
+      <name val="TH Sarabun New"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="TH Sarabun New"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="TH Sarabun New"/>
+      <b val="1"/>
+      <sz val="18"/>
     </font>
   </fonts>
   <fills count="7">
@@ -91,7 +112,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -113,11 +134,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -131,12 +196,43 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -502,20 +598,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ตารางราคา (แก้ไขได้ — ช่องเหลืองคือค่าที่ปรับได้)</t>
+          <t>ตารางราคา (แก้ไขได้ — ช่องเหลืองปรับได้)</t>
         </is>
       </c>
     </row>
@@ -559,6 +661,16 @@
         <v>600</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>VAT (%)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>7</v>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
@@ -579,12 +691,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>ช่วงเหมา (ใบ)</t>
+          <t>ช่วงเหมา(ใบ)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>เกิน (บ./ใบ)</t>
+          <t>เกิน(บ./ใบ)</t>
         </is>
       </c>
     </row>
@@ -655,7 +767,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>วัสดุ (กระดาษ = คิดตามแกรม×บ./กก.; สติ๊กเกอร์ = บ./ตร.ซม. รวม markup แล้ว)</t>
+          <t>วัสดุ</t>
         </is>
       </c>
     </row>
@@ -1025,120 +1137,819 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>อิงค์เจ็ท (บ./ตร.ม.)</t>
+          <t>อิงค์เจ็ท — วัสดุ &amp; เรตราคา (บ./ตร.ม.)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>ไวนิล: ช่วง(≤ตร.ม.) / 720 / 1440</t>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>ชื่อวัสดุ</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>โหมด</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>≤ตร.ม.</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>720(เล็ก)</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>1440(เล็ก)</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>2880(เล็ก)</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>720(ใหญ่)</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>1440(ใหญ่)</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>2880(ใหญ่)</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>flatปกติ</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>flatด่วน</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>ไวนิล Frontlit (ทึบแสง)</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B39" s="3" t="n">
+      <c r="D39" s="8" t="n">
         <v>180</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="E39" s="8" t="n">
         <v>220</v>
       </c>
+      <c r="F39" s="6" t="inlineStr"/>
+      <c r="G39" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr"/>
+      <c r="J39" s="6" t="inlineStr"/>
+      <c r="K39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
-        <v>100000</v>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="C40" s="3" t="n">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>ไวนิล Backlit (โปร่งแสง)</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr"/>
+      <c r="D40" s="6" t="inlineStr"/>
+      <c r="E40" s="6" t="inlineStr"/>
+      <c r="F40" s="6" t="inlineStr"/>
+      <c r="G40" s="6" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr"/>
+      <c r="I40" s="6" t="inlineStr"/>
+      <c r="J40" s="6" t="inlineStr"/>
+      <c r="K40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>ไวนิล Blockout (กันแสงทะลุ)</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr"/>
+      <c r="D41" s="6" t="inlineStr"/>
+      <c r="E41" s="6" t="inlineStr"/>
+      <c r="F41" s="6" t="inlineStr"/>
+      <c r="G41" s="6" t="inlineStr"/>
+      <c r="H41" s="6" t="inlineStr"/>
+      <c r="I41" s="6" t="inlineStr"/>
+      <c r="J41" s="6" t="inlineStr"/>
+      <c r="K41" s="6" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>สติ๊กเกอร์ PVC ขาว (Outdoor)</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" s="8" t="n">
         <v>150</v>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>สติ๊กเกอร์ PVC ใหญ่: ช่วง / 720 / 1440</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B42" s="3" t="n">
+      <c r="E42" s="8" t="n">
+        <v>190</v>
+      </c>
+      <c r="F42" s="6" t="inlineStr"/>
+      <c r="G42" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="H42" s="8" t="n">
         <v>150</v>
       </c>
-      <c r="C42" s="3" t="n">
-        <v>190</v>
-      </c>
+      <c r="I42" s="6" t="inlineStr"/>
+      <c r="J42" s="6" t="inlineStr"/>
+      <c r="K42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>100000</v>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>150</v>
-      </c>
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>สติ๊กเกอร์ PVC ใส (Clear)</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr"/>
+      <c r="D43" s="6" t="inlineStr"/>
+      <c r="E43" s="6" t="inlineStr"/>
+      <c r="F43" s="6" t="inlineStr"/>
+      <c r="G43" s="6" t="inlineStr"/>
+      <c r="H43" s="6" t="inlineStr"/>
+      <c r="I43" s="6" t="inlineStr"/>
+      <c r="J43" s="6" t="inlineStr"/>
+      <c r="K43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>วัสดุอื่น: ชื่อ / ปกติ / ด่วน</t>
-        </is>
-      </c>
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>สติ๊กเกอร์ Seethrough (One-Way Vision)</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr"/>
+      <c r="D44" s="6" t="inlineStr"/>
+      <c r="E44" s="6" t="inlineStr"/>
+      <c r="F44" s="6" t="inlineStr"/>
+      <c r="G44" s="6" t="inlineStr"/>
+      <c r="H44" s="6" t="inlineStr"/>
+      <c r="I44" s="6" t="inlineStr"/>
+      <c r="J44" s="6" t="inlineStr"/>
+      <c r="K44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>โฟโต้เปเปอร์</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="n">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>สติ๊กเกอร์ 3M (พรีเมียม/ถอดได้)</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr"/>
+      <c r="D45" s="6" t="inlineStr"/>
+      <c r="E45" s="6" t="inlineStr"/>
+      <c r="F45" s="6" t="inlineStr"/>
+      <c r="G45" s="6" t="inlineStr"/>
+      <c r="H45" s="6" t="inlineStr"/>
+      <c r="I45" s="6" t="inlineStr"/>
+      <c r="J45" s="6" t="inlineStr"/>
+      <c r="K45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>สติ๊กเกอร์ Backlit (ป้ายไฟ)</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr"/>
+      <c r="D46" s="6" t="inlineStr"/>
+      <c r="E46" s="6" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr"/>
+      <c r="G46" s="6" t="inlineStr"/>
+      <c r="H46" s="6" t="inlineStr"/>
+      <c r="I46" s="6" t="inlineStr"/>
+      <c r="J46" s="6" t="inlineStr"/>
+      <c r="K46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>PP Sticker (สังเคราะห์)</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr"/>
+      <c r="D47" s="6" t="inlineStr"/>
+      <c r="E47" s="6" t="inlineStr"/>
+      <c r="F47" s="6" t="inlineStr"/>
+      <c r="G47" s="6" t="inlineStr"/>
+      <c r="H47" s="6" t="inlineStr"/>
+      <c r="I47" s="6" t="inlineStr"/>
+      <c r="J47" s="6" t="inlineStr"/>
+      <c r="K47" s="6" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>โฟโต้เปเปอร์ (Glossy Photo)</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr"/>
+      <c r="D48" s="6" t="inlineStr"/>
+      <c r="E48" s="6" t="inlineStr"/>
+      <c r="F48" s="6" t="inlineStr"/>
+      <c r="G48" s="6" t="inlineStr"/>
+      <c r="H48" s="6" t="inlineStr"/>
+      <c r="I48" s="6" t="inlineStr"/>
+      <c r="J48" s="8" t="n">
         <v>250</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="K48" s="8" t="n">
         <v>350</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>ผ้าแคนวาส</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="n">
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>PP Paper (เคลือบ กันน้ำ)</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr"/>
+      <c r="D49" s="6" t="inlineStr"/>
+      <c r="E49" s="6" t="inlineStr"/>
+      <c r="F49" s="6" t="inlineStr"/>
+      <c r="G49" s="6" t="inlineStr"/>
+      <c r="H49" s="6" t="inlineStr"/>
+      <c r="I49" s="6" t="inlineStr"/>
+      <c r="J49" s="6" t="inlineStr"/>
+      <c r="K49" s="6" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Matte / Satin / Fine Art Paper</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr"/>
+      <c r="D50" s="6" t="inlineStr"/>
+      <c r="E50" s="6" t="inlineStr"/>
+      <c r="F50" s="6" t="inlineStr"/>
+      <c r="G50" s="6" t="inlineStr"/>
+      <c r="H50" s="6" t="inlineStr"/>
+      <c r="I50" s="6" t="inlineStr"/>
+      <c r="J50" s="6" t="inlineStr"/>
+      <c r="K50" s="6" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Blue Back Paper (หลังน้ำเงิน)</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr"/>
+      <c r="D51" s="6" t="inlineStr"/>
+      <c r="E51" s="6" t="inlineStr"/>
+      <c r="F51" s="6" t="inlineStr"/>
+      <c r="G51" s="6" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr"/>
+      <c r="I51" s="6" t="inlineStr"/>
+      <c r="J51" s="6" t="inlineStr"/>
+      <c r="K51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Film Backlit (ฟิล์มป้ายไฟ)</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr"/>
+      <c r="D52" s="6" t="inlineStr"/>
+      <c r="E52" s="6" t="inlineStr"/>
+      <c r="F52" s="6" t="inlineStr"/>
+      <c r="G52" s="6" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr"/>
+      <c r="I52" s="6" t="inlineStr"/>
+      <c r="J52" s="6" t="inlineStr"/>
+      <c r="K52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Clear / Reflective / Floor Film</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr"/>
+      <c r="D53" s="6" t="inlineStr"/>
+      <c r="E53" s="6" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr"/>
+      <c r="G53" s="6" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr"/>
+      <c r="I53" s="6" t="inlineStr"/>
+      <c r="J53" s="6" t="inlineStr"/>
+      <c r="K53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>ผ้า IT / ผ้าไวนิล (Backdrop)</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr"/>
+      <c r="D54" s="6" t="inlineStr"/>
+      <c r="E54" s="6" t="inlineStr"/>
+      <c r="F54" s="6" t="inlineStr"/>
+      <c r="G54" s="6" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr"/>
+      <c r="I54" s="6" t="inlineStr"/>
+      <c r="J54" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="K54" s="8" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>ผ้า Tension / Mesh</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr"/>
+      <c r="D55" s="6" t="inlineStr"/>
+      <c r="E55" s="6" t="inlineStr"/>
+      <c r="F55" s="6" t="inlineStr"/>
+      <c r="G55" s="6" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr"/>
+      <c r="I55" s="6" t="inlineStr"/>
+      <c r="J55" s="6" t="inlineStr"/>
+      <c r="K55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Dye-Sub Fabric (ซับลิเมชัน)</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr"/>
+      <c r="D56" s="6" t="inlineStr"/>
+      <c r="E56" s="6" t="inlineStr"/>
+      <c r="F56" s="6" t="inlineStr"/>
+      <c r="G56" s="6" t="inlineStr"/>
+      <c r="H56" s="6" t="inlineStr"/>
+      <c r="I56" s="6" t="inlineStr"/>
+      <c r="J56" s="6" t="inlineStr"/>
+      <c r="K56" s="6" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>ผ้าแคนวาส (Canvas)</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr"/>
+      <c r="D57" s="6" t="inlineStr"/>
+      <c r="E57" s="6" t="inlineStr"/>
+      <c r="F57" s="6" t="inlineStr"/>
+      <c r="G57" s="6" t="inlineStr"/>
+      <c r="H57" s="6" t="inlineStr"/>
+      <c r="I57" s="6" t="inlineStr"/>
+      <c r="J57" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="K57" s="8" t="n">
         <v>550</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>ผ้าป้าย/Backdrop</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n">
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Wallpaper (วอลเปเปอร์)</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr"/>
+      <c r="D58" s="6" t="inlineStr"/>
+      <c r="E58" s="6" t="inlineStr"/>
+      <c r="F58" s="6" t="inlineStr"/>
+      <c r="G58" s="6" t="inlineStr"/>
+      <c r="H58" s="6" t="inlineStr"/>
+      <c r="I58" s="6" t="inlineStr"/>
+      <c r="J58" s="6" t="inlineStr"/>
+      <c r="K58" s="6" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Magnetic (แม่เหล็ก)</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr"/>
+      <c r="D59" s="6" t="inlineStr"/>
+      <c r="E59" s="6" t="inlineStr"/>
+      <c r="F59" s="6" t="inlineStr"/>
+      <c r="G59" s="6" t="inlineStr"/>
+      <c r="H59" s="6" t="inlineStr"/>
+      <c r="I59" s="6" t="inlineStr"/>
+      <c r="J59" s="6" t="inlineStr"/>
+      <c r="K59" s="6" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Tarpaulin (ผ้าใบกันน้ำ)</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr"/>
+      <c r="D60" s="6" t="inlineStr"/>
+      <c r="E60" s="6" t="inlineStr"/>
+      <c r="F60" s="6" t="inlineStr"/>
+      <c r="G60" s="6" t="inlineStr"/>
+      <c r="H60" s="6" t="inlineStr"/>
+      <c r="I60" s="6" t="inlineStr"/>
+      <c r="J60" s="6" t="inlineStr"/>
+      <c r="K60" s="6" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Rigid Board (พิมพ์ UV ตรง)</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr"/>
+      <c r="D61" s="6" t="inlineStr"/>
+      <c r="E61" s="6" t="inlineStr"/>
+      <c r="F61" s="6" t="inlineStr"/>
+      <c r="G61" s="6" t="inlineStr"/>
+      <c r="H61" s="6" t="inlineStr"/>
+      <c r="I61" s="6" t="inlineStr"/>
+      <c r="J61" s="6" t="inlineStr"/>
+      <c r="K61" s="6" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Banner Mesh (ตาข่ายโฆษณา)</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr"/>
+      <c r="D62" s="6" t="inlineStr"/>
+      <c r="E62" s="6" t="inlineStr"/>
+      <c r="F62" s="6" t="inlineStr"/>
+      <c r="G62" s="6" t="inlineStr"/>
+      <c r="H62" s="6" t="inlineStr"/>
+      <c r="I62" s="6" t="inlineStr"/>
+      <c r="J62" s="6" t="inlineStr"/>
+      <c r="K62" s="6" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>งานหลังพิมพ์ (ยืนยันราคากับโรงงาน)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>ชื่อ</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>ราคา</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>หน่วย</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>ขั้นต่ำ(บ.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>— ไม่เลือก —</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>ชิ้น</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>เคลือบเงา</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>ใบ</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="C47" s="3" t="n">
-        <v>420</v>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>เคลือบด้าน</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>ใบ</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Spot UV</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>ใบ</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>พับ</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>ชิ้น</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>ไดคัท</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>ชิ้น</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>ปั๊มนูน</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>ชิ้น</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>ปั๊มเคทอง/เงิน</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>ชิ้น</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>รันนัมเบอร์</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>ชิ้น</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>ปรุฉีก</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>ชิ้น</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A37:D37"/>
+  <mergeCells count="5">
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A64:D64"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A37:K37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1150,12 +1961,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="3" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -1171,7 +1982,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>กรอกช่องเหลือง → ระบบเลือกเครื่องถูกกว่าให้ (ตัด4/ตัด2)</t>
+          <t>กรอกช่องเหลือง → ระบบเลือกเครื่องถูกกว่า (ตัด4/ตัด2) + งานหลังพิมพ์</t>
         </is>
       </c>
     </row>
@@ -1230,7 +2041,7 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>สีด้านหลัง (0 = หน้าเดียว)</t>
+          <t>สีด้านหลัง (0=หน้าเดียว)</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
@@ -1259,16 +2070,6 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>ค่าตกแต่ง/หลังพิมพ์ เพิ่ม (บาท)</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
@@ -1326,15 +2127,15 @@
     <row r="19">
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>จำนวนสี (เพลท)</t>
+          <t>สี (เพลท)</t>
         </is>
       </c>
       <c r="E19" s="6">
-        <f>IF(B10="Sheetwise",$B$8+$B$9,IF($B$9=0,$B$8,IF(B10="กลับหน้าในตัว",MAX($B$8,$B$9),$B$8+$B$9)))</f>
+        <f>IF($B$9=0,$B$8,IF($B$10="กลับหน้าในตัว",MAX($B$8,$B$9),$B$8+$B$9))</f>
         <v/>
       </c>
       <c r="F19" s="6">
-        <f>IF(B10="Sheetwise",$B$8+$B$9,IF($B$9=0,$B$8,IF(B10="กลับหน้าในตัว",MAX($B$8,$B$9),$B$8+$B$9)))</f>
+        <f>IF($B$9=0,$B$8,IF($B$10="กลับหน้าในตัว",MAX($B$8,$B$9),$B$8+$B$9))</f>
         <v/>
       </c>
     </row>
@@ -1371,7 +2172,7 @@
     <row r="22">
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>ใบพิมพ์ขั้นต่ำ</t>
+          <t>ใบขั้นต่ำ</t>
         </is>
       </c>
       <c r="E22" s="6">
@@ -1386,7 +2187,7 @@
     <row r="23">
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>เผื่อเสีย (ใบ)</t>
+          <t>เผื่อเสีย(ใบ)</t>
         </is>
       </c>
       <c r="E23" s="6">
@@ -1461,93 +2262,204 @@
     <row r="28">
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>ค่าตกแต่งเพิ่ม</t>
-        </is>
-      </c>
-      <c r="E28" s="12">
-        <f>$B$12</f>
-        <v/>
-      </c>
-      <c r="F28" s="12">
-        <f>$B$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>รวม (บาท)</t>
-        </is>
-      </c>
-      <c r="E29" s="13">
-        <f>E25+E26+E27+E28</f>
-        <v/>
-      </c>
-      <c r="F29" s="13">
-        <f>F25+F26+F27+F28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+          <t>รวม (ฐาน)</t>
+        </is>
+      </c>
+      <c r="E28" s="13">
+        <f>E25+E26+E27</f>
+        <v/>
+      </c>
+      <c r="F28" s="13">
+        <f>F25+F26+F27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ใบพิมพ์ (เครื่องที่เลือก)</t>
+        </is>
+      </c>
+      <c r="B30" s="2">
+        <f>IF(E28&lt;=F28,E24,F24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>งานหลังพิมพ์ (เลือกได้)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>รายการ</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>ราคา</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>งานหลังพิมพ์ 1</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="n"/>
+      <c r="C34" s="12">
+        <f>IFERROR(IF($B34="— ไม่เลือก —",0,MAX(VLOOKUP($B34,Prices!$A$66:$D$75,4,FALSE),VLOOKUP($B34,Prices!$A$66:$D$75,2,FALSE)*IF(VLOOKUP($B34,Prices!$A$66:$D$75,3,FALSE)="ใบ",$B$30,$B$11))),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>งานหลังพิมพ์ 2</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="12">
+        <f>IFERROR(IF($B35="— ไม่เลือก —",0,MAX(VLOOKUP($B35,Prices!$A$66:$D$75,4,FALSE),VLOOKUP($B35,Prices!$A$66:$D$75,2,FALSE)*IF(VLOOKUP($B35,Prices!$A$66:$D$75,3,FALSE)="ใบ",$B$30,$B$11))),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>งานหลังพิมพ์ 3</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="12">
+        <f>IFERROR(IF($B36="— ไม่เลือก —",0,MAX(VLOOKUP($B36,Prices!$A$66:$D$75,4,FALSE),VLOOKUP($B36,Prices!$A$66:$D$75,2,FALSE)*IF(VLOOKUP($B36,Prices!$A$66:$D$75,3,FALSE)="ใบ",$B$30,$B$11))),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>งานหลังพิมพ์ 4</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="12">
+        <f>IFERROR(IF($B37="— ไม่เลือก —",0,MAX(VLOOKUP($B37,Prices!$A$66:$D$75,4,FALSE),VLOOKUP($B37,Prices!$A$66:$D$75,2,FALSE)*IF(VLOOKUP($B37,Prices!$A$66:$D$75,3,FALSE)="ใบ",$B$30,$B$11))),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>อื่น ๆ เพิ่มเติม (บาท)</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>รวมงานหลังพิมพ์</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="13">
+        <f>SUM(C34:C38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>แนะนำเครื่อง</t>
         </is>
       </c>
-      <c r="B31" s="11">
-        <f>IF(E29&lt;=F29,"ตัด 4 (MO)","ตัด 2 (SM74)")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>ราคารวม (ถูกกว่า)</t>
-        </is>
-      </c>
-      <c r="B32" s="14">
-        <f>MIN(E29,F29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="B41" s="11">
+        <f>IF(E28&lt;=F28,"ตัด 4 (MO)","ตัด 2 (SM74)")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>ราคาฐาน (เพลท+พิมพ์+วัสดุ)</t>
+        </is>
+      </c>
+      <c r="B42" s="17">
+        <f>MIN(E28,F28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>ค่างานหลังพิมพ์</t>
+        </is>
+      </c>
+      <c r="B43" s="17">
+        <f>C39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>ราคารวม (บาท)</t>
+        </is>
+      </c>
+      <c r="B44" s="18">
+        <f>B42+B43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>ราคาต่อชิ้น</t>
         </is>
       </c>
-      <c r="B33" s="15">
-        <f>MIN(E29,F29)/$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>หมายเหตุ: กลับหน้าในตัว (W&amp;T) ใช้เมื่อสีหน้า=สีหลัง; สีต่างกันเลือก Sheetwise</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>ราคาโดยประมาณ ยังไม่รวม VAT/ค่าจัดส่ง</t>
+      <c r="B45" s="19">
+        <f>(B42+B43)/B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>หมายเหตุ: กลับหน้าในตัว (W&amp;T) ใช้เมื่อสีหน้า=สีหลัง; สีต่างกันเลือก Sheetwise · ราคายังไม่รวม VAT</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A36:F36"/>
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A32:C32"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>Prices!$A$19:$A$34</formula1>
     </dataValidation>
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"พิมพ์หน้าเดียว,กลับหน้าในตัว,Sheetwise"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B34 B35 B36 B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>Prices!$A$66:$A$75</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1560,11 +2472,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1582,7 +2494,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>ไวนิล</t>
+          <t>ไวนิล Frontlit (ทึบแสง)</t>
         </is>
       </c>
     </row>
@@ -1644,7 +2556,7 @@
           <t>พื้นที่รวม (ตร.ม.)</t>
         </is>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="20">
         <f>B5*B6*B7</f>
         <v/>
       </c>
@@ -1652,57 +2564,76 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>เรต (บ./ตร.ม.)</t>
-        </is>
-      </c>
-      <c r="B11" s="17">
-        <f>IF(B3="ไวนิล",IF(B10&lt;=Prices!$A$39,IF(B4=1440,Prices!$C$39,Prices!$B$39),IF(B4=1440,Prices!$C$40,Prices!$B$40)),IF(B3="สติ๊กเกอร์ PVC ใหญ่",IF(B10&lt;=Prices!$A$42,IF(B4=1440,Prices!$C$42,Prices!$B$42),IF(B4=1440,Prices!$C$43,Prices!$B$43)),IF(B3="โฟโต้เปเปอร์",IF(B8="ใช่",Prices!$C$45,Prices!$B$45),IF(B3="ผ้าแคนวาส",IF(B8="ใช่",Prices!$C$46,Prices!$B$46),IF(B8="ใช่",Prices!$C$47,Prices!$B$47)))))</f>
+          <t>โหมดราคา</t>
+        </is>
+      </c>
+      <c r="B11" s="10">
+        <f>IFERROR(VLOOKUP(B3,Prices!$A$39:$K$62,2,FALSE),"quote")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>เรต (บ./ตร.ม.)</t>
+        </is>
+      </c>
+      <c r="B12" s="17">
+        <f>IFERROR(IF(B11="quote","สอบถามราคา",IF(B11="flat",IF(B8="ใช่",VLOOKUP(B3,Prices!$A$39:$K$62,11,FALSE),VLOOKUP(B3,Prices!$A$39:$K$62,10,FALSE)),IF(B10&lt;=VLOOKUP(B3,Prices!$A$39:$K$62,3,FALSE),CHOOSE(MATCH(--B4,{720,1440,2880},0),VLOOKUP(B3,Prices!$A$39:$K$62,4,FALSE),VLOOKUP(B3,Prices!$A$39:$K$62,5,FALSE),VLOOKUP(B3,Prices!$A$39:$K$62,6,FALSE)),CHOOSE(MATCH(--B4,{720,1440,2880},0),VLOOKUP(B3,Prices!$A$39:$K$62,7,FALSE),VLOOKUP(B3,Prices!$A$39:$K$62,8,FALSE),VLOOKUP(B3,Prices!$A$39:$K$62,9,FALSE))))),"สอบถามราคา")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>ค่างานด่วน (เพิ่ม)</t>
         </is>
       </c>
-      <c r="B12" s="17">
-        <f>IF(AND(OR(B3="ไวนิล",B3="สติ๊กเกอร์ PVC ใหญ่"),B8="ใช่",B10&gt;=1,B10&lt;50),IF(B4=1440,50,20)*B10,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="B13" s="17">
+        <f>IF(AND(B11="volume",B8="ใช่",B10&gt;=1,B10&lt;50),IF(--B4&gt;=1440,50,20)*B10,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>ราคารวม (บาท)</t>
         </is>
       </c>
-      <c r="B14" s="14">
-        <f>B11*B10+B12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="B15" s="18">
+        <f>IF(ISNUMBER(B12),B12*B10+B13,"สอบถามราคากับฝ่ายขาย 081-770-7544")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>ราคาต่อป้าย</t>
         </is>
       </c>
-      <c r="B15" s="18">
-        <f>(B11*B10+B12)/B7</f>
-        <v/>
+      <c r="B16" s="21">
+        <f>IF(ISNUMBER(B12),(B12*B10+B13)/B7,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>หมายเหตุ: วัสดุที่เป็น “สอบถามราคา” ยังไม่มีเรตในระบบ — โทร 081-770-7544 / LINE @thaiprint.co.th</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A18:D18"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"ไวนิล,สติ๊กเกอร์ PVC ใหญ่,โฟโต้เปเปอร์,ผ้าแคนวาส,ผ้าป้าย/Backdrop"</formula1>
+      <formula1>Prices!$A$39:$A$62</formula1>
     </dataValidation>
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"720,1440"</formula1>
+      <formula1>"720,1440,2880"</formula1>
     </dataValidation>
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"ใช่,ไม่"</formula1>
@@ -1710,4 +2641,272 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="B1" s="23" t="inlineStr">
+        <is>
+          <t>บริษัท ไทยพริ้นท์ อินเตอร์กรุ๊ป จำกัด</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>โรงพิมพ์ฉลากสินค้าและกล่องบรรจุภัณฑ์ · โทร 02-149-4518, 081-770-7544</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>89/38 หมู่ 8 ต.เสาธงหิน อ.บางใหญ่ นนทบุรี 11140 · เลขผู้เสียภาษี 0125564010433</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>ใบเสนอราคา / QUOTATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>เลขที่เอกสาร</t>
+        </is>
+      </c>
+      <c r="B7" s="7">
+        <f>"QT"&amp;TEXT(TODAY(),"yymmdd")&amp;"-001"</f>
+        <v/>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>วันที่</t>
+        </is>
+      </c>
+      <c r="E7" s="25">
+        <f>TODAY()</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ลูกค้า</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>โทร</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ชื่องาน</t>
+        </is>
+      </c>
+      <c r="B9" s="6">
+        <f>"งานพิมพ์ "&amp;Offset!B4</f>
+        <v/>
+      </c>
+      <c r="C9" s="26" t="n"/>
+      <c r="D9" s="26" t="n"/>
+      <c r="E9" s="14" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10">
+        <f>CONCATENATE("วัสดุ: ",Offset!B4," | ขนาด: ",Offset!B6," × ",Offset!B7," ซม. | สี หน้า/หลัง: ",Offset!B8,"/",Offset!B9," | เครื่อง: ",Offset!B41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>รายการ</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>จำนวน</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>หน่วย</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>ราคา/หน่วย</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>รวม (บาท)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>ค่างานพิมพ์ (เพลท+พิมพ์+วัสดุ)</t>
+        </is>
+      </c>
+      <c r="B14" s="28">
+        <f>Offset!B11</f>
+        <v/>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>ชิ้น</t>
+        </is>
+      </c>
+      <c r="D14" s="12">
+        <f>Offset!B42/Offset!B11</f>
+        <v/>
+      </c>
+      <c r="E14" s="12">
+        <f>Offset!B42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>ค่างานหลังพิมพ์</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="12">
+        <f>Offset!B43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr"/>
+      <c r="B16" s="6" t="inlineStr"/>
+      <c r="C16" s="6" t="inlineStr"/>
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr"/>
+      <c r="B17" s="6" t="inlineStr"/>
+      <c r="C17" s="6" t="inlineStr"/>
+      <c r="D17" s="6" t="inlineStr"/>
+      <c r="E17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="D18" s="29" t="inlineStr">
+        <is>
+          <t>รวมเป็นเงิน</t>
+        </is>
+      </c>
+      <c r="E18" s="12">
+        <f>Offset!B42+Offset!B43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="D19" s="30" t="inlineStr">
+        <is>
+          <t>VAT (Prices!B7 %)</t>
+        </is>
+      </c>
+      <c r="E19" s="12">
+        <f>(Offset!B42+Offset!B43)*Prices!$B$7/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="D20" s="31" t="inlineStr">
+        <is>
+          <t>ราคารวมทั้งสิ้น</t>
+        </is>
+      </c>
+      <c r="E20" s="32">
+        <f>(Offset!B42+Offset!B43)*(1+Prices!$B$7/100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>หมายเหตุ: ราคาประเมินเบื้องต้น ยืนราคา 15 วัน · ราคาอาจเปลี่ยนตามแบบจริง/งานตกแต่งพิเศษ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>ผู้เสนอราคา</t>
+        </is>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>ผู้อนุมัติ/ลูกค้า</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="33" t="inlineStr">
+        <is>
+          <t>__________________</t>
+        </is>
+      </c>
+      <c r="D26" s="33" t="inlineStr">
+        <is>
+          <t>__________________</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A22:E22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>